--- a/data/trans_bre/P6906-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 16,29</t>
+          <t>-10,29; 14,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 15,04</t>
+          <t>-17,76; 15,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 30,33</t>
+          <t>-16,6; 33,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 23,36</t>
+          <t>-12,07; 23,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 199,44</t>
+          <t>-71,9; 171,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 105,87</t>
+          <t>-63,1; 115,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,22; 199,59</t>
+          <t>-63,64; 257,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 566,86</t>
+          <t>-60,94; 483,1</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 9,31</t>
+          <t>-8,18; 10,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 16,8</t>
+          <t>-3,43; 17,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 22,66</t>
+          <t>3,31; 22,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 12,66</t>
+          <t>-5,12; 12,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 42,35</t>
+          <t>-32,65; 50,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 75,67</t>
+          <t>-13,45; 78,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,69; 141,26</t>
+          <t>13,88; 145,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 92,26</t>
+          <t>-23,54; 94,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 4,87</t>
+          <t>-26,57; 4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 18,09</t>
+          <t>-21,04; 18,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 10,43</t>
+          <t>-26,01; 9,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 20,72</t>
+          <t>-8,25; 22,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 19,82</t>
+          <t>-64,29; 20,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 77,46</t>
+          <t>-48,32; 87,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 31,89</t>
+          <t>-49,31; 26,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 112,63</t>
+          <t>-24,71; 130,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,66</t>
+          <t>-7,47; 6,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 12,0</t>
+          <t>-4,97; 11,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 16,56</t>
+          <t>0,5; 17,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 12,9</t>
+          <t>-2,28; 13,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 28,61</t>
+          <t>-29,74; 33,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 54,34</t>
+          <t>-17,72; 51,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 78,46</t>
+          <t>2,09; 84,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 80,48</t>
+          <t>-11,12; 81,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6906-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,07</t>
+          <t>8,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 14,86</t>
+          <t>-9,06; 16,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 15,93</t>
+          <t>-19,11; 13,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 33,61</t>
+          <t>-13,52; 32,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 23,74</t>
+          <t>-8,3; 26,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,9; 171,01</t>
+          <t>-65,49; 225,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,1; 115,39</t>
+          <t>-65,66; 84,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,64; 257,25</t>
+          <t>-54,13; 240,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 483,1</t>
+          <t>-46,54; 423,53</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 10,0</t>
+          <t>-8,58; 10,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 17,46</t>
+          <t>-4,53; 16,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 22,49</t>
+          <t>3,7; 22,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 12,98</t>
+          <t>-1,0; 14,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 50,5</t>
+          <t>-33,43; 49,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 78,64</t>
+          <t>-16,52; 79,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,88; 145,99</t>
+          <t>15,54; 148,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 94,69</t>
+          <t>-4,86; 97,66</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 4,0</t>
+          <t>-25,56; 5,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 18,46</t>
+          <t>-22,74; 16,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 9,15</t>
+          <t>-25,41; 10,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 22,66</t>
+          <t>-11,19; 20,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 20,42</t>
+          <t>-64,18; 22,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 87,35</t>
+          <t>-53,52; 71,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 26,2</t>
+          <t>-48,21; 34,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 130,37</t>
+          <t>-28,42; 109,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,84</t>
+          <t>-7,67; 5,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 11,83</t>
+          <t>-4,87; 11,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 17,02</t>
+          <t>0,63; 16,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 13,0</t>
+          <t>1,27; 14,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 33,56</t>
+          <t>-31,36; 29,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 51,86</t>
+          <t>-16,05; 50,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 84,59</t>
+          <t>2,08; 80,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 81,47</t>
+          <t>4,94; 82,52</t>
         </is>
       </c>
     </row>
